--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104562_W12.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104562_W12.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>D. NEEDHAM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9005</v>
+        <v>3.9221</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5484</v>
+        <v>3.792</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3521</v>
+        <v>0.1301</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.471</v>
+        <v>4.4366</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.375</v>
+        <v>1.979</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0959</v>
+        <v>2.4576</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9116</v>
+        <v>4.819</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.0906</v>
+        <v>1.7064</v>
       </c>
       <c r="L2" t="n">
-        <v>1.0021</v>
+        <v>3.1126</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.3825</v>
+        <v>-0.3824</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2844</v>
+        <v>0.2725</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.0981</v>
+        <v>-0.6549</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5983</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4911</v>
+        <v>0.3388</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1072</v>
+        <v>0.3452</v>
       </c>
       <c r="V2" t="n">
-        <v>1.639</v>
+        <v>-2.3367</v>
       </c>
       <c r="W2" t="n">
-        <v>2.5068</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.8678</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. VILDOZA</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2915</v>
+        <v>3.9166</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1603</v>
+        <v>2.8667</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1312</v>
+        <v>1.0499</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.9451</v>
+        <v>-0.4781</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.948</v>
+        <v>-0.3843</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9971</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.3275</v>
+        <v>0.8792</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.1917</v>
+        <v>-0.1109</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.1357</v>
+        <v>0.9901</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6176</v>
+        <v>-1.3573</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7563</v>
+        <v>-0.2734</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1387</v>
+        <v>-1.0838</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8147</v>
+        <v>2.5039</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3046</v>
+        <v>1.6223</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2098</v>
+        <v>0.8589</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0948</v>
+        <v>0.7634</v>
       </c>
       <c r="V3" t="n">
-        <v>3.1173</v>
+        <v>1.6342</v>
       </c>
       <c r="W3" t="n">
-        <v>3.278</v>
+        <v>2.4945</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1607</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="4">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2851</v>
+        <v>3.8752</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2724</v>
+        <v>3.777</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0127</v>
+        <v>0.0982</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5119</v>
+        <v>2.5058</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1472</v>
+        <v>1.146</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3647</v>
+        <v>1.3598</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6867</v>
+        <v>3.6647</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7144</v>
+        <v>1.7064</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9724</v>
+        <v>1.9582</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1749</v>
+        <v>-1.1588</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5672</v>
+        <v>-0.5604</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3876</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1735</v>
+        <v>0.7058</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2141</v>
+        <v>0.2766</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. NEEDHAM</t>
+          <t>P. VILDOZA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.8126</v>
+        <v>3.8001</v>
       </c>
       <c r="E5" t="n">
-        <v>3.7487</v>
+        <v>1.9547</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0639</v>
+        <v>1.8454</v>
       </c>
       <c r="G5" t="n">
-        <v>4.4441</v>
+        <v>-2.9641</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9812</v>
+        <v>-1.9473</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4629</v>
+        <v>-1.0168</v>
       </c>
       <c r="J5" t="n">
-        <v>4.8436</v>
+        <v>-2.3632</v>
       </c>
       <c r="K5" t="n">
-        <v>1.7144</v>
+        <v>-1.2001</v>
       </c>
       <c r="L5" t="n">
-        <v>3.1292</v>
+        <v>-1.1631</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3994</v>
+        <v>-0.6009</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2669</v>
+        <v>-0.7472</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6663</v>
+        <v>0.1463</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1342</v>
+        <v>1.8211</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4952</v>
+        <v>1.8211</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5804</v>
+        <v>1.8325</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2662</v>
+        <v>1.0494</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3142</v>
+        <v>0.7831</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.3461</v>
+        <v>3.1107</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>3.2684</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.3461</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6231</v>
+        <v>2.2566</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1677</v>
+        <v>2.8008</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5445</v>
+        <v>-0.5442</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3525</v>
+        <v>-0.3532</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7563</v>
+        <v>0.7472</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1088</v>
+        <v>-1.1005</v>
       </c>
       <c r="J6" t="n">
-        <v>0.865</v>
+        <v>0.8477</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4648</v>
+        <v>1.4511</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5998</v>
+        <v>-0.6035</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2176</v>
+        <v>-1.2009</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7086</v>
+        <v>-0.7039</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.509</v>
+        <v>-0.497</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8169</v>
+        <v>1.4505</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3176</v>
+        <v>0.9822</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4993</v>
+        <v>0.4683</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W6" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="7">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1379</v>
+        <v>1.1589</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1669</v>
+        <v>-0.1193</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3049</v>
+        <v>1.2783</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6054</v>
+        <v>-0.6048</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7228</v>
+        <v>-0.7319</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1174</v>
+        <v>0.127</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6301</v>
+        <v>-0.6529</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6274</v>
+        <v>-0.6452</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0027</v>
+        <v>-0.0077</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0247</v>
+        <v>0.0481</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0954</v>
+        <v>-0.0866</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1201</v>
+        <v>0.1347</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9533</v>
+        <v>0.9639</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5293</v>
+        <v>0.6034</v>
       </c>
       <c r="U7" t="n">
-        <v>0.424</v>
+        <v>0.3605</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.4783</v>
+        <v>-1.4764</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. SUSINSKAS</t>
+          <t>P. BUSQUETS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5762</v>
+        <v>0.6757</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9071</v>
+        <v>0.4353</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3309</v>
+        <v>0.2404</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4442</v>
+        <v>-2.2331</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.446</v>
+        <v>-0.5139</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8902</v>
+        <v>-1.7193</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3446</v>
+        <v>-0.8021</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1212</v>
+        <v>0.4202</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2233</v>
+        <v>-1.2223</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9003</v>
+        <v>-1.431</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5672</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3331</v>
+        <v>-0.497</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5878</v>
+        <v>2.2763</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7295</v>
+        <v>1.4551</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5626</v>
+        <v>0.9705</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1669</v>
+        <v>0.4846</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.1853</v>
+        <v>0.3155</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.405</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.1853</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. BUSQUETS</t>
+          <t>M. SUSINSKAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0396</v>
+        <v>0.6705</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1351</v>
+        <v>1.7257</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1747</v>
+        <v>-1.0552</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.2233</v>
+        <v>0.4386</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5093</v>
+        <v>-0.4398</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.714</v>
+        <v>0.8783</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7689</v>
+        <v>1.3265</v>
       </c>
       <c r="K9" t="n">
-        <v>0.436</v>
+        <v>0.1207</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.205</v>
+        <v>1.2058</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4543</v>
+        <v>-0.8879</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9453</v>
+        <v>-0.5604</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.509</v>
+        <v>-0.3275</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2683</v>
+        <v>1.5934</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8072</v>
+        <v>0.8174</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3539</v>
+        <v>0.3992</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4533</v>
+        <v>0.4182</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3214</v>
+        <v>-2.1789</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4141</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. FERRANDO</t>
+          <t>O. LIVINGSTON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4934</v>
+        <v>0.3537</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0106</v>
+        <v>0.5763</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4827</v>
+        <v>-0.2225</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.954</v>
+        <v>-1.2327</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3622</v>
+        <v>0.2478</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5918</v>
+        <v>-1.4805</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.749</v>
+        <v>-0.0911</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.1477</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.749</v>
+        <v>-0.2388</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.205</v>
+        <v>-1.1416</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3622</v>
+        <v>0.1002</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1573</v>
+        <v>-1.2417</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2268</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.5039</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2268</v>
+        <v>2.0487</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6194</v>
+        <v>0.2497</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5777</v>
+        <v>0.1321</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0417</v>
+        <v>0.1176</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3856</v>
+        <v>1.792</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1607</v>
+        <v>3.0392</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5463</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O. LIVINGSTON</t>
+          <t>G. FERRANDO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6787</v>
+        <v>-0.4767</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2674</v>
+        <v>-0.0629</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4114</v>
+        <v>-0.4138</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.2218</v>
+        <v>-0.9537</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2629</v>
+        <v>-0.3592</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4847</v>
+        <v>-0.5945</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0601</v>
+        <v>-0.7524</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1692</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.2293</v>
+        <v>-0.7524</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1617</v>
+        <v>-0.2012</v>
       </c>
       <c r="N11" t="n">
-        <v>0.09370000000000001</v>
+        <v>-0.3592</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.2554</v>
+        <v>0.1579</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.4952</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0415</v>
+        <v>0.2276</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.803</v>
+        <v>0.6363</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7652</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0378</v>
+        <v>0.1046</v>
       </c>
       <c r="V11" t="n">
-        <v>1.7997</v>
+        <v>-0.387</v>
       </c>
       <c r="W11" t="n">
-        <v>3.0531</v>
+        <v>0.1578</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2534</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2147</v>
+        <v>-2.1739</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6383</v>
+        <v>-1.7697</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5764</v>
+        <v>-0.4042</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2162</v>
+        <v>-0.2145</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6927</v>
+        <v>0.6895</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9089</v>
+        <v>-0.904</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1914</v>
+        <v>0.1839</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0795</v>
+        <v>0.0722</v>
       </c>
       <c r="L12" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4077</v>
+        <v>-0.3984</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6132</v>
+        <v>0.6173</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.0209</v>
+        <v>-1.0157</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2284</v>
+        <v>0.2682</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4386</v>
+        <v>0.3227</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2102</v>
+        <v>-0.0545</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>17.2797</v>
+        <v>17.9788</v>
       </c>
       <c r="E13" t="n">
-        <v>15.5863</v>
+        <v>15.9766</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6936</v>
+        <v>2.0024</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.589100000000001</v>
+        <v>-1.653199999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>0.477</v>
+        <v>0.4330999999999998</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.066</v>
+        <v>-2.086600000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>7.3073</v>
+        <v>7.0593</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7898</v>
+        <v>3.6685</v>
       </c>
       <c r="L13" t="n">
-        <v>3.5175</v>
+        <v>3.3906</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.8963</v>
+        <v>-8.712300000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.3128</v>
+        <v>-3.2351</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.5834</v>
+        <v>-5.4771</v>
       </c>
       <c r="P13" t="n">
-        <v>7.939100000000002</v>
+        <v>7.967100000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-11.3417</v>
+        <v>-11.3816</v>
       </c>
       <c r="R13" t="n">
-        <v>19.2809</v>
+        <v>19.3486</v>
       </c>
       <c r="S13" t="n">
-        <v>10.2226</v>
+        <v>10.9623</v>
       </c>
       <c r="T13" t="n">
-        <v>6.1551</v>
+        <v>6.894800000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>4.067499999999999</v>
+        <v>4.067600000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>0.7070000000000012</v>
+        <v>0.7026000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>13.4658</v>
+        <v>13.4041</v>
       </c>
       <c r="X13" t="n">
-        <v>-12.7588</v>
+        <v>-12.7016</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.0198</v>
+        <v>7.7715</v>
       </c>
       <c r="E14" t="n">
-        <v>9.6927</v>
+        <v>9.989599999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.673</v>
+        <v>-2.2181</v>
       </c>
       <c r="G14" t="n">
-        <v>3.5882</v>
+        <v>3.5993</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6881</v>
+        <v>0.6974</v>
       </c>
       <c r="I14" t="n">
-        <v>2.9001</v>
+        <v>2.9018</v>
       </c>
       <c r="J14" t="n">
-        <v>5.4979</v>
+        <v>5.472</v>
       </c>
       <c r="K14" t="n">
-        <v>1.697</v>
+        <v>1.6892</v>
       </c>
       <c r="L14" t="n">
-        <v>3.8009</v>
+        <v>3.7828</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.9097</v>
+        <v>-1.8728</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.0089</v>
+        <v>-0.9918</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9008</v>
+        <v>-0.881</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.7123</v>
+        <v>-1.958</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3217</v>
+        <v>-0.969</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.3907</v>
+        <v>-0.989</v>
       </c>
       <c r="V14" t="n">
-        <v>5.4633</v>
+        <v>5.4474</v>
       </c>
       <c r="W14" t="n">
-        <v>6.8775</v>
+        <v>6.8524</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. DIAGNE</t>
+          <t>O. PAULI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7311</v>
+        <v>1.5886</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1455</v>
+        <v>2.4198</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5856</v>
+        <v>-0.8312</v>
       </c>
       <c r="G15" t="n">
-        <v>3.4812</v>
+        <v>1.8661</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1514</v>
+        <v>0.4421</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3298</v>
+        <v>1.424</v>
       </c>
       <c r="J15" t="n">
-        <v>2.4592</v>
+        <v>1.7034</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1531</v>
+        <v>-0.2176</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3061</v>
+        <v>1.921</v>
       </c>
       <c r="M15" t="n">
-        <v>1.022</v>
+        <v>0.1627</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0017</v>
+        <v>0.6597</v>
       </c>
       <c r="O15" t="n">
-        <v>1.0237</v>
+        <v>-0.497</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.2683</v>
+        <v>1.1382</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.6293</v>
+        <v>-0.2276</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6109</v>
+        <v>-1.4156</v>
       </c>
       <c r="T15" t="n">
-        <v>1.3157</v>
+        <v>-0.6902</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7047</v>
+        <v>-0.7254</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.6342</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. PAULI</t>
+          <t>M. SANZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7010999999999999</v>
+        <v>0.3942</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0991</v>
+        <v>0.58</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.398</v>
+        <v>-0.1858</v>
       </c>
       <c r="G16" t="n">
-        <v>1.8646</v>
+        <v>2.1593</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4386</v>
+        <v>1.0911</v>
       </c>
       <c r="I16" t="n">
-        <v>1.426</v>
+        <v>1.0683</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7304</v>
+        <v>3.2308</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2047</v>
+        <v>2.2408</v>
       </c>
       <c r="L16" t="n">
-        <v>1.9351</v>
+        <v>0.9901</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1343</v>
+        <v>-1.0715</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6433</v>
+        <v>-1.1497</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.509</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2268</v>
+        <v>-2.5039</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.2977</v>
+        <v>-0.4692</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0434</v>
+        <v>-0.3046</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.2543</v>
+        <v>-0.1645</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="W16" t="n">
-        <v>1.639</v>
+        <v>0.1578</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.639</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="17">
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0636</v>
+        <v>-0.092</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1642</v>
+        <v>0.1576</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2278</v>
+        <v>-0.2496</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4506</v>
+        <v>0.4524</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3117</v>
+        <v>-0.3103</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7623</v>
+        <v>0.7627</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4424</v>
+        <v>0.4364</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4078</v>
+        <v>0.4019</v>
       </c>
       <c r="M17" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.016</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3463</v>
+        <v>-0.3447</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1780,28 +1780,28 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3536</v>
+        <v>-0.3867</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2782</v>
+        <v>-0.2788</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.1078</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. SANZ</t>
+          <t>A. DIAGNE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2805</v>
+        <v>-0.2446</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7314000000000001</v>
+        <v>-1.1775</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0118</v>
+        <v>0.9329</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1486</v>
+        <v>3.4951</v>
       </c>
       <c r="H18" t="n">
-        <v>1.085</v>
+        <v>1.1544</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0636</v>
+        <v>2.3407</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2533</v>
+        <v>2.4442</v>
       </c>
       <c r="K18" t="n">
-        <v>2.2512</v>
+        <v>1.1409</v>
       </c>
       <c r="L18" t="n">
-        <v>1.0021</v>
+        <v>1.3033</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1047</v>
+        <v>1.0509</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1662</v>
+        <v>0.0135</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0614</v>
+        <v>1.0374</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.4952</v>
+        <v>-3.6421</v>
       </c>
       <c r="R18" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1342</v>
+        <v>-0.3739</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1875</v>
+        <v>0.0205</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9467</v>
+        <v>-0.3943</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3214</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6681</v>
+        <v>-1.9179</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2187</v>
+        <v>-1.2231</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4495</v>
+        <v>-0.6948</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9235</v>
+        <v>-0.9191</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1559</v>
+        <v>-0.1551</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7675999999999999</v>
+        <v>-0.764</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0546</v>
+        <v>0.0545</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9781</v>
+        <v>-0.9736</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.805</v>
+        <v>-0.8012</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3895</v>
+        <v>0.1394</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.2788</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. SHURNA</t>
+          <t>M. EJIM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3656</v>
+        <v>-2.1617</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.184</v>
+        <v>-2.254</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1816</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.5097</v>
+        <v>-3.4232</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0043</v>
+        <v>-2.1597</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.514</v>
+        <v>-1.2634</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6971000000000001</v>
+        <v>-2.811</v>
       </c>
       <c r="K20" t="n">
-        <v>0.052</v>
+        <v>-1.4694</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.749</v>
+        <v>-1.3416</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8126</v>
+        <v>-0.6122</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0477</v>
+        <v>-0.6904</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7649</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.5039</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.2763</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8559</v>
+        <v>-0.8476</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4869</v>
+        <v>-0.523</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.369</v>
+        <v>-0.3246</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>2.3367</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.584</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. EJIM</t>
+          <t>J. SHURNA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0778</v>
+        <v>-2.3597</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.7767</v>
+        <v>-1.1886</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3011</v>
+        <v>-1.1711</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.4168</v>
+        <v>-1.5004</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.1586</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2582</v>
+        <v>-1.5087</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.768</v>
+        <v>-0.7007</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.4484</v>
+        <v>0.0517</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3196</v>
+        <v>-0.7524</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6488</v>
+        <v>-0.7997</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7103</v>
+        <v>-0.0433</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0614</v>
+        <v>-0.7563</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.4952</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.2683</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.7802</v>
+        <v>-0.8593</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.113</v>
+        <v>-0.4879</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6672</v>
+        <v>-0.3714</v>
       </c>
       <c r="V21" t="n">
-        <v>2.3461</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>3.5994</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6918</v>
+        <v>-3.8591</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6981000000000001</v>
+        <v>0.6926</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.3898</v>
+        <v>-4.5517</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3006</v>
+        <v>-0.2886</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3407</v>
+        <v>-0.3336</v>
       </c>
       <c r="I22" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8156</v>
+        <v>0.8137</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0693</v>
+        <v>0.0689</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7463</v>
+        <v>0.7447</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1162</v>
+        <v>-1.1023</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4099</v>
+        <v>-0.4025</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7063</v>
+        <v>-0.6998</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.408</v>
+        <v>-0.598</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2782</v>
+        <v>-0.2788</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1298</v>
+        <v>-0.3191</v>
       </c>
       <c r="V22" t="n">
-        <v>-3.6636</v>
+        <v>-3.6554</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X22" t="n">
-        <v>-3.8243</v>
+        <v>-3.8132</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.8696</v>
+        <v>-4.3517</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5445</v>
+        <v>-2.2163</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.3252</v>
+        <v>-2.1354</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1131</v>
+        <v>-0.1082</v>
       </c>
       <c r="H23" t="n">
-        <v>1.4356</v>
+        <v>1.4442</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.5487</v>
+        <v>-1.5523</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3499</v>
+        <v>0.332</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.9136</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5679</v>
+        <v>-0.5816</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.463</v>
+        <v>-0.4402</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5178</v>
+        <v>0.5306</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5032</v>
+        <v>-0.9963</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6261</v>
+        <v>-0.272</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8771</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.7148</v>
+        <v>-9.6805</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.5007</v>
+        <v>-7.7825</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.2141</v>
+        <v>-1.898</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.6805</v>
+        <v>-3.6795</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.3131</v>
+        <v>-2.3121</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.3674</v>
+        <v>-1.3675</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.2421</v>
+        <v>-2.2629</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.2264</v>
+        <v>-1.2345</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.0157</v>
+        <v>-1.0284</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.4384</v>
+        <v>-1.4166</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.0867</v>
+        <v>-1.0775</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3517</v>
+        <v>-0.3391</v>
       </c>
       <c r="P24" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="Q24" t="n">
-        <v>-5.6708</v>
+        <v>-5.6908</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1781</v>
+        <v>-0.1312</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0907</v>
+        <v>-0.1443</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2689</v>
+        <v>0.013</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W24" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-17.2798</v>
+        <v>-14.9129</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.693599999999999</v>
+        <v>-2.002399999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-15.5863</v>
+        <v>-12.9105</v>
       </c>
       <c r="G25" t="n">
-        <v>1.588999999999999</v>
+        <v>1.653199999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.4769999999999994</v>
+        <v>-0.4332000000000003</v>
       </c>
       <c r="I25" t="n">
-        <v>2.065900000000001</v>
+        <v>2.086500000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>8.896099999999999</v>
+        <v>8.712400000000002</v>
       </c>
       <c r="K25" t="n">
-        <v>3.3128</v>
+        <v>3.235300000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>5.5834</v>
+        <v>5.477</v>
       </c>
       <c r="M25" t="n">
-        <v>-7.306999999999999</v>
+        <v>-7.0593</v>
       </c>
       <c r="N25" t="n">
-        <v>-3.7898</v>
+        <v>-3.6685</v>
       </c>
       <c r="O25" t="n">
-        <v>-3.5174</v>
+        <v>-3.390600000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>-7.9391</v>
+        <v>-7.9671</v>
       </c>
       <c r="Q25" t="n">
-        <v>-19.2808</v>
+        <v>-19.3486</v>
       </c>
       <c r="R25" t="n">
-        <v>11.3416</v>
+        <v>11.3816</v>
       </c>
       <c r="S25" t="n">
-        <v>-10.2228</v>
+        <v>-7.896399999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.0677</v>
+        <v>-4.0675</v>
       </c>
       <c r="U25" t="n">
-        <v>-6.155000000000001</v>
+        <v>-3.8286</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.7070999999999994</v>
+        <v>-0.7025999999999997</v>
       </c>
       <c r="W25" t="n">
-        <v>12.7587</v>
+        <v>12.7017</v>
       </c>
       <c r="X25" t="n">
-        <v>-13.4658</v>
+        <v>-13.4041</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104562_W12.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104562_W12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104562_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104562_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104562_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104562_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104562_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104562_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104562_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104562_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104562_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104562_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104562_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-12.7016</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104562_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104562_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104562_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104562_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104562_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104562_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104562_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104562_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-3.8132</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104562_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104562_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104562_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-13.4041</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
